--- a/artfynd/A 30969-2022 artfynd.xlsx
+++ b/artfynd/A 30969-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30969-2022 artfynd.xlsx
+++ b/artfynd/A 30969-2022 artfynd.xlsx
@@ -1997,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123581863</v>
+        <v>123581866</v>
       </c>
       <c r="B13" t="n">
-        <v>58186</v>
+        <v>58196</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2036,10 +2036,14 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2121,10 +2125,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123581866</v>
+        <v>123581863</v>
       </c>
       <c r="B14" t="n">
-        <v>58190</v>
+        <v>58192</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2137,21 +2141,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103057</v>
+        <v>103055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2160,14 +2164,10 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>

--- a/artfynd/A 30969-2022 artfynd.xlsx
+++ b/artfynd/A 30969-2022 artfynd.xlsx
@@ -1997,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123581866</v>
+        <v>123581863</v>
       </c>
       <c r="B13" t="n">
-        <v>58196</v>
+        <v>58195</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103057</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2036,14 +2036,10 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2125,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123581863</v>
+        <v>123581866</v>
       </c>
       <c r="B14" t="n">
-        <v>58192</v>
+        <v>58199</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2141,21 +2137,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2164,10 +2160,14 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>

--- a/artfynd/A 30969-2022 artfynd.xlsx
+++ b/artfynd/A 30969-2022 artfynd.xlsx
@@ -1997,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123581863</v>
+        <v>123581866</v>
       </c>
       <c r="B13" t="n">
-        <v>58195</v>
+        <v>58200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2036,10 +2036,14 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2121,10 +2125,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123581866</v>
+        <v>123581863</v>
       </c>
       <c r="B14" t="n">
-        <v>58199</v>
+        <v>58196</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2137,21 +2141,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103057</v>
+        <v>103055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2160,14 +2164,10 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>

--- a/artfynd/A 30969-2022 artfynd.xlsx
+++ b/artfynd/A 30969-2022 artfynd.xlsx
@@ -1997,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123581866</v>
+        <v>123581863</v>
       </c>
       <c r="B13" t="n">
-        <v>58200</v>
+        <v>58196</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103057</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2036,14 +2036,10 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2125,10 +2121,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123581863</v>
+        <v>123581866</v>
       </c>
       <c r="B14" t="n">
-        <v>58196</v>
+        <v>58200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2141,21 +2137,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2164,10 +2160,14 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>

--- a/artfynd/A 30969-2022 artfynd.xlsx
+++ b/artfynd/A 30969-2022 artfynd.xlsx
@@ -1997,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123581863</v>
+        <v>123581866</v>
       </c>
       <c r="B13" t="n">
-        <v>58196</v>
+        <v>58200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2036,10 +2036,14 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2121,10 +2125,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123581866</v>
+        <v>123581863</v>
       </c>
       <c r="B14" t="n">
-        <v>58200</v>
+        <v>58196</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2137,21 +2141,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103057</v>
+        <v>103055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2160,14 +2164,10 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
